--- a/database_cong_trinh.xlsx
+++ b/database_cong_trinh.xlsx
@@ -17951,21 +17951,21 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>SCL Đường dây và trạm biến áp năm 2026</t>
+          <t>Sửa chữa lớn TSCĐ thay thế LBFCO, FCO, LA... ngăn ngừa sự cố năm 2026</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>12552889759</v>
+        <v>0</v>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
@@ -18008,17 +18008,17 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>Mười hai tỷ năm trăm năm mươi hai triệu tám trăm tám mươi chín nghìn bảy trăm năm mươi chín đồng</t>
+          <t>Không đồng</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>thuê ngoài</t>
+          <t>tự thực hiện</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>Công ty điện lực Vũng Tàu</t>
+          <t>Công ty Điện lực Vũng Tàu</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -18049,7 +18049,7 @@
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="n">
-        <v>11225612598</v>
+        <v>0</v>
       </c>
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
@@ -18066,12 +18066,12 @@
       <c r="W354" t="inlineStr"/>
       <c r="X354" t="inlineStr"/>
       <c r="Y354" t="n">
-        <v>113440831</v>
+        <v>196215944</v>
       </c>
       <c r="Z354" t="inlineStr"/>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>11225612598</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -18103,7 +18103,7 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="n">
-        <v>10205102362</v>
+        <v>0</v>
       </c>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
@@ -18120,12 +18120,12 @@
       <c r="W355" t="inlineStr"/>
       <c r="X355" t="inlineStr"/>
       <c r="Y355" t="n">
-        <v>103128028</v>
+        <v>178378131</v>
       </c>
       <c r="Z355" t="inlineStr"/>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>10205102362</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr"/>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -18211,7 +18211,7 @@
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="n">
-        <v>10205102362</v>
+        <v>0</v>
       </c>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
@@ -18228,12 +18228,12 @@
       <c r="W357" t="inlineStr"/>
       <c r="X357" t="inlineStr"/>
       <c r="Y357" t="n">
-        <v>103128028</v>
+        <v>178378131</v>
       </c>
       <c r="Z357" t="inlineStr"/>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>10101974334</t>
+          <t>-178378131</t>
         </is>
       </c>
       <c r="AB357" t="inlineStr"/>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -18427,7 +18427,7 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="n">
-        <v>1020510236</v>
+        <v>0</v>
       </c>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
@@ -18444,12 +18444,12 @@
       <c r="W361" t="inlineStr"/>
       <c r="X361" t="inlineStr"/>
       <c r="Y361" t="n">
-        <v>10312803</v>
+        <v>17837813</v>
       </c>
       <c r="Z361" t="inlineStr"/>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>1020510236</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -18481,7 +18481,7 @@
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="n">
-        <v>1020638174</v>
+        <v>0</v>
       </c>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
@@ -18503,7 +18503,7 @@
       <c r="Z362" t="inlineStr"/>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>1020638174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB362" t="inlineStr"/>
@@ -18525,7 +18525,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="n">
-        <v>945035346</v>
+        <v>0</v>
       </c>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
@@ -18557,7 +18557,7 @@
       <c r="Z363" t="inlineStr"/>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>945035346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr"/>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -18589,7 +18589,7 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="n">
-        <v>945035346</v>
+        <v>0</v>
       </c>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       <c r="Z364" t="inlineStr"/>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>945035346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr"/>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -18795,7 +18795,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -19065,7 +19065,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -19173,7 +19173,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -19291,7 +19291,7 @@
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="n">
-        <v>945035346</v>
+        <v>0</v>
       </c>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
@@ -19313,7 +19313,7 @@
       <c r="Z377" t="inlineStr"/>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>945035346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB377" t="inlineStr"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -19345,7 +19345,7 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="n">
-        <v>75602828</v>
+        <v>0</v>
       </c>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
@@ -19367,7 +19367,7 @@
       <c r="Z378" t="inlineStr"/>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>75602828</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB378" t="inlineStr"/>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -19399,7 +19399,7 @@
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="n">
-        <v>869395028</v>
+        <v>0</v>
       </c>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
@@ -19421,7 +19421,7 @@
       <c r="Z379" t="inlineStr"/>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>869395028</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB379" t="inlineStr"/>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -19453,7 +19453,7 @@
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="n">
-        <v>804995396</v>
+        <v>0</v>
       </c>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
@@ -19475,7 +19475,7 @@
       <c r="Z380" t="inlineStr"/>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>804995396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB380" t="inlineStr"/>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -19723,7 +19723,7 @@
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="n">
-        <v>64399632</v>
+        <v>0</v>
       </c>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       <c r="Z385" t="inlineStr"/>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>64399632</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB385" t="inlineStr"/>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -19777,7 +19777,7 @@
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="n">
-        <v>597756655</v>
+        <v>0</v>
       </c>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
@@ -19799,7 +19799,7 @@
       <c r="Z386" t="inlineStr"/>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>597756655</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB386" t="inlineStr"/>
@@ -19816,12 +19816,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Tổng giá trị trước thuế</t>
+          <t>Tổng giá trị sau thuế</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -19831,7 +19831,7 @@
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="n">
-        <v>13713402455</v>
+        <v>0</v>
       </c>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
@@ -19848,12 +19848,12 @@
       <c r="W387" t="inlineStr"/>
       <c r="X387" t="inlineStr"/>
       <c r="Y387" t="n">
-        <v>113440831</v>
+        <v>196215944</v>
       </c>
       <c r="Z387" t="inlineStr"/>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>13713402455</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB387" t="inlineStr"/>
@@ -19870,12 +19870,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Tổng giá trị thuế GTGT</t>
+          <t>Tổng giá trị trước thuế</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -19885,7 +19885,7 @@
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="n">
-        <v>12552889759</v>
+        <v>0</v>
       </c>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
@@ -19902,12 +19902,12 @@
       <c r="W388" t="inlineStr"/>
       <c r="X388" t="inlineStr"/>
       <c r="Y388" t="n">
-        <v>103128028</v>
+        <v>178378131</v>
       </c>
       <c r="Z388" t="inlineStr"/>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>12552889759</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB388" t="inlineStr"/>
@@ -19924,12 +19924,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Tổng giá trị sau thuế</t>
+          <t>Thuế GTGT</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -19939,7 +19939,7 @@
       <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="n">
-        <v>1160512696</v>
+        <v>0</v>
       </c>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
@@ -19956,12 +19956,12 @@
       <c r="W389" t="inlineStr"/>
       <c r="X389" t="inlineStr"/>
       <c r="Y389" t="n">
-        <v>10312803</v>
+        <v>17837813</v>
       </c>
       <c r="Z389" t="inlineStr"/>
       <c r="AA389" t="inlineStr">
         <is>
-          <t>1160512696</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB389" t="inlineStr"/>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606002</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -20047,7 +20047,7 @@
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
       <c r="J391" t="n">
-        <v>12552889759</v>
+        <v>0</v>
       </c>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
@@ -20064,12 +20064,12 @@
       <c r="W391" t="inlineStr"/>
       <c r="X391" t="inlineStr"/>
       <c r="Y391" t="n">
-        <v>103128028</v>
+        <v>178378131</v>
       </c>
       <c r="Z391" t="inlineStr"/>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>12552889759</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB391" t="inlineStr"/>
@@ -20081,21 +20081,21 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>VII</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Sửa chữa lớn TSCĐ thay thế LBFCO, FCO, LA... ngăn ngừa sự cố năm 2026</t>
+          <t>SCL Hệ thống điện bằng biện pháp Live-Line 2026</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0</v>
+        <v>5780025934</v>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="Z392" t="inlineStr">
         <is>
-          <t>Không đồng</t>
+          <t>Năm tỷ bảy trăm tám mươi triệu không trăm hai mươi lăm nghìn chín trăm ba mươi bốn đồng</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Vũng Tàu</t>
+          <t>Công ty điện lực Vũng Tàu</t>
         </is>
       </c>
       <c r="AC392" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -20196,7 +20196,7 @@
       <c r="W393" t="inlineStr"/>
       <c r="X393" t="inlineStr"/>
       <c r="Y393" t="n">
-        <v>196215944</v>
+        <v>0</v>
       </c>
       <c r="Z393" t="inlineStr"/>
       <c r="AA393" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -20250,7 +20250,7 @@
       <c r="W394" t="inlineStr"/>
       <c r="X394" t="inlineStr"/>
       <c r="Y394" t="n">
-        <v>178378131</v>
+        <v>0</v>
       </c>
       <c r="Z394" t="inlineStr"/>
       <c r="AA394" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -20358,12 +20358,12 @@
       <c r="W396" t="inlineStr"/>
       <c r="X396" t="inlineStr"/>
       <c r="Y396" t="n">
-        <v>178378131</v>
+        <v>0</v>
       </c>
       <c r="Z396" t="inlineStr"/>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>-178378131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB396" t="inlineStr"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -20574,7 +20574,7 @@
       <c r="W400" t="inlineStr"/>
       <c r="X400" t="inlineStr"/>
       <c r="Y400" t="n">
-        <v>17837813</v>
+        <v>0</v>
       </c>
       <c r="Z400" t="inlineStr"/>
       <c r="AA400" t="inlineStr">
@@ -20601,7 +20601,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -20655,7 +20655,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -20763,7 +20763,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -21087,7 +21087,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -21141,7 +21141,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -21195,7 +21195,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -21249,7 +21249,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -21465,7 +21465,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -21681,7 +21681,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -21897,7 +21897,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -21946,12 +21946,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Tổng giá trị sau thuế</t>
+          <t>Tổng giá trị trước thuế</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -21978,7 +21978,7 @@
       <c r="W426" t="inlineStr"/>
       <c r="X426" t="inlineStr"/>
       <c r="Y426" t="n">
-        <v>196215944</v>
+        <v>0</v>
       </c>
       <c r="Z426" t="inlineStr"/>
       <c r="AA426" t="inlineStr">
@@ -22000,12 +22000,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Tổng giá trị trước thuế</t>
+          <t>Tổng giá trị thuế GTGT</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -22032,7 +22032,7 @@
       <c r="W427" t="inlineStr"/>
       <c r="X427" t="inlineStr"/>
       <c r="Y427" t="n">
-        <v>178378131</v>
+        <v>0</v>
       </c>
       <c r="Z427" t="inlineStr"/>
       <c r="AA427" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Thuế GTGT</t>
+          <t>Tổng giá trị sau thuế</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -22086,7 +22086,7 @@
       <c r="W428" t="inlineStr"/>
       <c r="X428" t="inlineStr"/>
       <c r="Y428" t="n">
-        <v>17837813</v>
+        <v>0</v>
       </c>
       <c r="Z428" t="inlineStr"/>
       <c r="AA428" t="inlineStr">
@@ -22113,7 +22113,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -22167,7 +22167,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -22194,7 +22194,7 @@
       <c r="W430" t="inlineStr"/>
       <c r="X430" t="inlineStr"/>
       <c r="Y430" t="n">
-        <v>178378131</v>
+        <v>0</v>
       </c>
       <c r="Z430" t="inlineStr"/>
       <c r="AA430" t="inlineStr">
@@ -22211,21 +22211,21 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>II</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SCL Hệ thống điện bằng biện pháp Live-Line 2026</t>
+          <t>SCL Đường dây và trạm biến áp năm 2026</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>5780025934</v>
+        <v>12552889759</v>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr"/>
@@ -22268,12 +22268,12 @@
       </c>
       <c r="Z431" t="inlineStr">
         <is>
-          <t>Năm tỷ bảy trăm tám mươi triệu không trăm hai mươi lăm nghìn chín trăm ba mươi bốn đồng</t>
+          <t>Mười hai tỷ năm trăm năm mươi hai triệu tám trăm tám mươi chín nghìn bảy trăm năm mươi chín đồng</t>
         </is>
       </c>
       <c r="AA431" t="inlineStr">
         <is>
-          <t>tự thực hiện</t>
+          <t>thuê ngoài</t>
         </is>
       </c>
       <c r="AB431" t="inlineStr">
@@ -22282,7 +22282,22 @@
         </is>
       </c>
       <c r="AC431" t="inlineStr"/>
-      <c r="AD431" t="inlineStr"/>
+      <c r="AD431" t="inlineStr">
+        <is>
+          <t>1. Hạng mục lưới hạ thế: 
+- máy cắt 3p 230/380v 250a od+thùng b.vệ: 7 Bộ
+- Hộp domino 9 cực.: 1036 Cái
+- Hộp đầu cáp ngầm hạ thế 3x240+1x120mm2: 114 Bộ
+- Hộp đầu cáp ngầm hạ thế 3x50+1x25mm2: 15 Bộ
+- Hộp đầu cáp ngầm hạ thế 3x95+1x50mm2: 29 Bộ
+- trụ bê tông ly tâm 6m 100kg: 3 Cái
+- trụ bê tông (2 đoạn) 8m: 1 Cái
+- trụ bê tông ly tâm 10m: 6 Cái
+- Trụ bê tông ly tâm Thủ Đức-PC-8,5m-2kN-1đoạn: 40 Cái
+2. Dán decal 174 tủ RMU ngoài trời.
+3.  Sữa chữa 18 tủ RMU ngoài trời bị rỉ sét</t>
+        </is>
+      </c>
       <c r="AE431" t="inlineStr"/>
       <c r="AF431" t="inlineStr"/>
     </row>
@@ -22299,7 +22314,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -22309,7 +22324,7 @@
       <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr"/>
       <c r="J432" t="n">
-        <v>0</v>
+        <v>11225612598</v>
       </c>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr"/>
@@ -22326,11 +22341,11 @@
       <c r="W432" t="inlineStr"/>
       <c r="X432" t="inlineStr"/>
       <c r="Y432" t="n">
-        <v>0</v>
+        <v>113440831</v>
       </c>
       <c r="Z432" t="inlineStr"/>
       <c r="AA432" t="n">
-        <v>0</v>
+        <v>11225612598</v>
       </c>
       <c r="AB432" t="inlineStr"/>
       <c r="AC432" t="inlineStr"/>
@@ -22351,7 +22366,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -22361,7 +22376,7 @@
       <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="n">
-        <v>0</v>
+        <v>10205102362</v>
       </c>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr"/>
@@ -22378,11 +22393,11 @@
       <c r="W433" t="inlineStr"/>
       <c r="X433" t="inlineStr"/>
       <c r="Y433" t="n">
-        <v>0</v>
+        <v>103128028</v>
       </c>
       <c r="Z433" t="inlineStr"/>
       <c r="AA433" t="n">
-        <v>0</v>
+        <v>10205102362</v>
       </c>
       <c r="AB433" t="inlineStr"/>
       <c r="AC433" t="inlineStr"/>
@@ -22403,7 +22418,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -22455,7 +22470,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -22465,7 +22480,7 @@
       <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr"/>
       <c r="J435" t="n">
-        <v>0</v>
+        <v>10205102362</v>
       </c>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
@@ -22482,11 +22497,11 @@
       <c r="W435" t="inlineStr"/>
       <c r="X435" t="inlineStr"/>
       <c r="Y435" t="n">
-        <v>0</v>
+        <v>103128028</v>
       </c>
       <c r="Z435" t="inlineStr"/>
       <c r="AA435" t="n">
-        <v>0</v>
+        <v>10101974334</v>
       </c>
       <c r="AB435" t="inlineStr"/>
       <c r="AC435" t="inlineStr"/>
@@ -22507,7 +22522,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -22559,7 +22574,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -22611,7 +22626,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -22663,7 +22678,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -22673,7 +22688,7 @@
       <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="n">
-        <v>0</v>
+        <v>1020510236</v>
       </c>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
@@ -22690,11 +22705,11 @@
       <c r="W439" t="inlineStr"/>
       <c r="X439" t="inlineStr"/>
       <c r="Y439" t="n">
-        <v>0</v>
+        <v>10312803</v>
       </c>
       <c r="Z439" t="inlineStr"/>
       <c r="AA439" t="n">
-        <v>0</v>
+        <v>1020510236</v>
       </c>
       <c r="AB439" t="inlineStr"/>
       <c r="AC439" t="inlineStr"/>
@@ -22715,7 +22730,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -22725,7 +22740,7 @@
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="n">
-        <v>0</v>
+        <v>1020638174</v>
       </c>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
@@ -22746,7 +22761,7 @@
       </c>
       <c r="Z440" t="inlineStr"/>
       <c r="AA440" t="n">
-        <v>0</v>
+        <v>1020638174</v>
       </c>
       <c r="AB440" t="inlineStr"/>
       <c r="AC440" t="inlineStr"/>
@@ -22767,7 +22782,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -22777,7 +22792,7 @@
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
       <c r="J441" t="n">
-        <v>0</v>
+        <v>945035346</v>
       </c>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
@@ -22798,7 +22813,7 @@
       </c>
       <c r="Z441" t="inlineStr"/>
       <c r="AA441" t="n">
-        <v>0</v>
+        <v>945035346</v>
       </c>
       <c r="AB441" t="inlineStr"/>
       <c r="AC441" t="inlineStr"/>
@@ -22819,7 +22834,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -22829,7 +22844,7 @@
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="n">
-        <v>0</v>
+        <v>945035346</v>
       </c>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
@@ -22850,7 +22865,7 @@
       </c>
       <c r="Z442" t="inlineStr"/>
       <c r="AA442" t="n">
-        <v>0</v>
+        <v>945035346</v>
       </c>
       <c r="AB442" t="inlineStr"/>
       <c r="AC442" t="inlineStr"/>
@@ -22871,7 +22886,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -22923,7 +22938,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -22975,7 +22990,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -23027,7 +23042,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -23079,7 +23094,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
@@ -23131,7 +23146,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
@@ -23183,7 +23198,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D449" t="inlineStr"/>
@@ -23235,7 +23250,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
@@ -23287,7 +23302,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -23339,7 +23354,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -23391,7 +23406,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -23443,7 +23458,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -23495,7 +23510,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -23505,7 +23520,7 @@
       <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="n">
-        <v>0</v>
+        <v>945035346</v>
       </c>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
@@ -23526,7 +23541,7 @@
       </c>
       <c r="Z455" t="inlineStr"/>
       <c r="AA455" t="n">
-        <v>0</v>
+        <v>945035346</v>
       </c>
       <c r="AB455" t="inlineStr"/>
       <c r="AC455" t="inlineStr"/>
@@ -23547,7 +23562,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -23557,7 +23572,7 @@
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="n">
-        <v>0</v>
+        <v>75602828</v>
       </c>
       <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr"/>
@@ -23578,7 +23593,7 @@
       </c>
       <c r="Z456" t="inlineStr"/>
       <c r="AA456" t="n">
-        <v>0</v>
+        <v>75602828</v>
       </c>
       <c r="AB456" t="inlineStr"/>
       <c r="AC456" t="inlineStr"/>
@@ -23599,7 +23614,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
@@ -23609,7 +23624,7 @@
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="n">
-        <v>0</v>
+        <v>869395028</v>
       </c>
       <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr"/>
@@ -23630,7 +23645,7 @@
       </c>
       <c r="Z457" t="inlineStr"/>
       <c r="AA457" t="n">
-        <v>0</v>
+        <v>869395028</v>
       </c>
       <c r="AB457" t="inlineStr"/>
       <c r="AC457" t="inlineStr"/>
@@ -23651,7 +23666,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
@@ -23661,7 +23676,7 @@
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr"/>
       <c r="J458" t="n">
-        <v>0</v>
+        <v>804995396</v>
       </c>
       <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr"/>
@@ -23682,7 +23697,7 @@
       </c>
       <c r="Z458" t="inlineStr"/>
       <c r="AA458" t="n">
-        <v>0</v>
+        <v>804995396</v>
       </c>
       <c r="AB458" t="inlineStr"/>
       <c r="AC458" t="inlineStr"/>
@@ -23703,7 +23718,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -23755,7 +23770,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
@@ -23807,7 +23822,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
@@ -23859,7 +23874,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
@@ -23911,7 +23926,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D463" t="inlineStr"/>
@@ -23921,7 +23936,7 @@
       <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr"/>
       <c r="J463" t="n">
-        <v>0</v>
+        <v>64399632</v>
       </c>
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr"/>
@@ -23942,7 +23957,7 @@
       </c>
       <c r="Z463" t="inlineStr"/>
       <c r="AA463" t="n">
-        <v>0</v>
+        <v>64399632</v>
       </c>
       <c r="AB463" t="inlineStr"/>
       <c r="AC463" t="inlineStr"/>
@@ -23963,7 +23978,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
@@ -23973,7 +23988,7 @@
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr"/>
       <c r="J464" t="n">
-        <v>0</v>
+        <v>597756655</v>
       </c>
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
@@ -23994,7 +24009,7 @@
       </c>
       <c r="Z464" t="inlineStr"/>
       <c r="AA464" t="n">
-        <v>0</v>
+        <v>597756655</v>
       </c>
       <c r="AB464" t="inlineStr"/>
       <c r="AC464" t="inlineStr"/>
@@ -24015,7 +24030,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D465" t="inlineStr"/>
@@ -24025,7 +24040,7 @@
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr"/>
       <c r="J465" t="n">
-        <v>0</v>
+        <v>13713402455</v>
       </c>
       <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr"/>
@@ -24042,11 +24057,11 @@
       <c r="W465" t="inlineStr"/>
       <c r="X465" t="inlineStr"/>
       <c r="Y465" t="n">
-        <v>0</v>
+        <v>113440831</v>
       </c>
       <c r="Z465" t="inlineStr"/>
       <c r="AA465" t="n">
-        <v>0</v>
+        <v>13713402455</v>
       </c>
       <c r="AB465" t="inlineStr"/>
       <c r="AC465" t="inlineStr"/>
@@ -24067,7 +24082,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -24077,7 +24092,7 @@
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr"/>
       <c r="J466" t="n">
-        <v>0</v>
+        <v>12552889759</v>
       </c>
       <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr"/>
@@ -24094,11 +24109,11 @@
       <c r="W466" t="inlineStr"/>
       <c r="X466" t="inlineStr"/>
       <c r="Y466" t="n">
-        <v>0</v>
+        <v>103128028</v>
       </c>
       <c r="Z466" t="inlineStr"/>
       <c r="AA466" t="n">
-        <v>0</v>
+        <v>12552889759</v>
       </c>
       <c r="AB466" t="inlineStr"/>
       <c r="AC466" t="inlineStr"/>
@@ -24119,7 +24134,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D467" t="inlineStr"/>
@@ -24129,7 +24144,7 @@
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr"/>
       <c r="J467" t="n">
-        <v>0</v>
+        <v>1160512696</v>
       </c>
       <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr"/>
@@ -24146,11 +24161,11 @@
       <c r="W467" t="inlineStr"/>
       <c r="X467" t="inlineStr"/>
       <c r="Y467" t="n">
-        <v>0</v>
+        <v>10312803</v>
       </c>
       <c r="Z467" t="inlineStr"/>
       <c r="AA467" t="n">
-        <v>0</v>
+        <v>1160512696</v>
       </c>
       <c r="AB467" t="inlineStr"/>
       <c r="AC467" t="inlineStr"/>
@@ -24171,7 +24186,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
@@ -24223,7 +24238,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>VTAD2610002</t>
+          <t>VTAD2605001</t>
         </is>
       </c>
       <c r="D469" t="inlineStr"/>
@@ -24233,7 +24248,7 @@
       <c r="H469" t="inlineStr"/>
       <c r="I469" t="inlineStr"/>
       <c r="J469" t="n">
-        <v>0</v>
+        <v>12552889759</v>
       </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
@@ -24250,11 +24265,11 @@
       <c r="W469" t="inlineStr"/>
       <c r="X469" t="inlineStr"/>
       <c r="Y469" t="n">
-        <v>0</v>
+        <v>103128028</v>
       </c>
       <c r="Z469" t="inlineStr"/>
       <c r="AA469" t="n">
-        <v>0</v>
+        <v>12552889759</v>
       </c>
       <c r="AB469" t="inlineStr"/>
       <c r="AC469" t="inlineStr"/>

--- a/database_cong_trinh.xlsx
+++ b/database_cong_trinh.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sửa chữa lớn TSCĐ thay thế LBFCO,FCO,LA ngăn ngừa sự cố 2026</t>
+          <t>Sửa chữa lớn TSCĐ thay thế LBFCO, FCO, LA... ngăn ngừa sự cố năm 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sửa chữa nhà đặt MPĐ, nhà máy An Hội, Đặc khu công đảo</t>
+          <t>Sửa chữa nhà đặt máy phát điện, nhà máy An Hội, Đặc khu Côn Đảo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SCL Hệ thống điện bằng biện pháp Live-Line 2026</t>
+          <t>Sửa chữa lớn hệ thống điện bằng biện pháp Live-Line năm 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SCL Công Xa Công ty Điện lực Vũng Tàu 2026</t>
+          <t>Sửa chữa lớn công xa Công ty Điện lực Vũng Tàu năm 2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sửa chữa lớn Công xa 2026</t>
+          <t>Sửa chữa lớn công xa Công ty Điện lực Vũng Tàu năm 2026</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SCL MPĐ Cummins G1,G2 NMĐ An Hội 2026</t>
+          <t>Sửa chữa lớn máy phát điện Cummins G1, G2 nhà máy điện An hội năm 2026</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Sửa chữa lớn Công xa 2026</t>
+          <t>Sửa chữa lớn công xa Công ty Điện lực Vũng Tàu năm 2026</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Sửa chữa lớn TSCĐ thay thế LBFCO,FCO,LA ngăn ngừa sự cố 2026</t>
+          <t>Sửa chữa lớn TSCĐ thay thế LBFCO, FCO, LA... ngăn ngừa sự cố năm 2026</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SCL Hệ thống điện bằng biện pháp Live-Line 2026</t>
+          <t>Sửa chữa lớn hệ thống điện bằng biện pháp Live-Line năm 2026</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SCL Đường dây và trạm biến áp năm 2026</t>
+          <t>Sửa chữa lớn đường dây trung, hạ thế và trạm biến áp năm 2026</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
